--- a/archive/legacy_runs/lr_estimation_2025_07_21/est_lrs_by_category_plusminus_filled.xlsx
+++ b/archive/legacy_runs/lr_estimation_2025_07_21/est_lrs_by_category_plusminus_filled.xlsx
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="C2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.077</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="D6" t="n">
         <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>0.35</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.05</v>
+        <v>0.71</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="F9" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.756</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8</v>
+        <v>0.28</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>0.25</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="C14" t="n">
         <v>0.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C15" t="n">
         <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="C16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.6</v>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="D17" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3</v>
+        <v>0.71</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4</v>
+        <v>0.22</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>0.65</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G22" t="n">
         <v>1.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>0.95</v>
+        <v>0.51</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C25" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="F25" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H25" t="n">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="26">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>2.75</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27">
@@ -1245,28 +1245,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E27" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="29">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.95</v>
+        <v>0.34</v>
       </c>
       <c r="D29" t="n">
-        <v>1.05</v>
+        <v>0.2</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G29" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H29" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="30">
@@ -1341,25 +1341,25 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="D30" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8</v>
+        <v>0.155</v>
       </c>
       <c r="H30" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="31">
@@ -1369,25 +1369,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="D31" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="I31" t="n">
         <v>0.9</v>
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C32" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G32" t="n">
         <v>0.8</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="I32" t="n">
-        <v>0.45</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -1431,28 +1431,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="C33" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="F33" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.6</v>
       </c>
-      <c r="F34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.95</v>
-      </c>
       <c r="H34" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="35">
@@ -1493,28 +1493,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="C35" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1.3</v>
+        <v>0.707</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
@@ -1524,28 +1524,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="C36" t="n">
         <v>0.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="37">
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H37" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="I37" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
@@ -1586,28 +1586,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H38" t="n">
         <v>0.6</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39">
@@ -1617,28 +1617,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C39" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H39" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="40">
@@ -1648,28 +1648,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.25</v>
+        <v>0.71</v>
       </c>
       <c r="F40" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="41">
@@ -1679,28 +1679,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.95</v>
+        <v>0.727</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="H41" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="42">
@@ -1710,28 +1710,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="C42" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="43">
@@ -1741,28 +1741,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="C43" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D43" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="44">
@@ -1772,28 +1772,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="C44" t="n">
-        <v>1.05</v>
+        <v>0.65</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H44" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="45">
@@ -1803,28 +1803,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.97</v>
+        <v>0.3</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E45" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="46">
@@ -1834,28 +1834,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D46" t="n">
         <v>0.3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G46" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="47">
@@ -1865,28 +1865,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="E47" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="48">
@@ -1896,28 +1896,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C48" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>0.8</v>
       </c>
       <c r="G48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="49">
@@ -1927,28 +1927,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G49" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
@@ -1958,28 +1958,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E50" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G50" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1989,28 +1989,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C51" t="n">
         <v>0.7</v>
       </c>
       <c r="D51" t="n">
-        <v>1.3</v>
+        <v>0.65</v>
       </c>
       <c r="E51" t="n">
-        <v>0.45</v>
+        <v>1.2</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H51" t="n">
-        <v>1.3</v>
+        <v>0.65</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="52">
@@ -2020,28 +2020,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="C52" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E52" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2051,28 +2051,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D53" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F53" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="54">
@@ -2082,28 +2082,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="C54" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E54" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G54" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="55">
@@ -2113,28 +2113,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="F55" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="G55" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="H55" t="n">
-        <v>0.95</v>
+        <v>0.521</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="56">
@@ -2144,28 +2144,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="G56" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="H56" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2175,28 +2175,28 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D57" t="n">
         <v>0.6</v>
       </c>
-      <c r="C57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.05</v>
-      </c>
       <c r="E57" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="G57" t="n">
-        <v>1.05</v>
+        <v>0.45</v>
       </c>
       <c r="H57" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E58" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="59">
@@ -2237,28 +2237,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="C59" t="n">
-        <v>1.2</v>
+        <v>0.63</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="F59" t="n">
-        <v>1.2</v>
+        <v>0.23</v>
       </c>
       <c r="G59" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="60">
@@ -2268,28 +2268,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="F60" t="n">
-        <v>1.6</v>
-      </c>
       <c r="G60" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="H60" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="I60" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="61">
@@ -2299,28 +2299,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D61" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>0.71</v>
       </c>
       <c r="H61" t="n">
-        <v>1.8</v>
+        <v>0.45</v>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="62">
@@ -2330,25 +2330,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E62" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="F62" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="G62" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="H62" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="I62" t="n">
         <v>0.4</v>
@@ -2361,28 +2361,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="C63" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E63" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="G63" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="64">
@@ -2392,28 +2392,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D64" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H64" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="65">
@@ -2423,28 +2423,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C65" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D65" t="n">
-        <v>1.1</v>
+        <v>0.35</v>
       </c>
       <c r="E65" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="F65" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="G65" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="66">
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E66" t="n">
         <v>0.2</v>
@@ -2469,13 +2469,13 @@
         <v>0.4</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="67">
@@ -2485,28 +2485,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C67" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="D67" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G67" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H67" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
@@ -2516,28 +2516,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E68" t="n">
         <v>0.6</v>
       </c>
-      <c r="E68" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.3</v>
       </c>
-      <c r="G68" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.9</v>
-      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="69">
@@ -2547,28 +2547,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="C69" t="n">
-        <v>1.15</v>
+        <v>0.4</v>
       </c>
       <c r="D69" t="n">
-        <v>1.1</v>
+        <v>0.65</v>
       </c>
       <c r="E69" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F69" t="n">
-        <v>1.05</v>
+        <v>0.28</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9</v>
+        <v>0.432</v>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="70">
@@ -2578,28 +2578,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E70" t="n">
         <v>0.4</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H70" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="71">
@@ -2609,28 +2609,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="D71" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="E71" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="G71" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H71" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2643,25 +2643,25 @@
         <v>1.2</v>
       </c>
       <c r="C72" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F72" t="n">
         <v>1.2</v>
       </c>
       <c r="G72" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H72" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="73">
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E73" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>0.8</v>
       </c>
       <c r="H73" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="I73" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2702,28 +2702,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="C74" t="n">
         <v>1.8</v>
       </c>
       <c r="D74" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G74" t="n">
         <v>1.1</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1.8</v>
       </c>
       <c r="H74" t="n">
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="75">
@@ -2733,28 +2733,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D75" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H75" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="76">
@@ -2764,28 +2764,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D76" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="E76" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F76" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H76" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="77">
@@ -2798,25 +2798,25 @@
         <v>0.8</v>
       </c>
       <c r="C77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E77" t="n">
         <v>0.9</v>
       </c>
-      <c r="D77" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.95</v>
-      </c>
       <c r="F77" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="G77" t="n">
         <v>0.8</v>
       </c>
       <c r="H77" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
@@ -2826,28 +2826,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C78" t="n">
         <v>2.5</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F78" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="G78" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="79">
@@ -2857,28 +2857,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C79" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="D79" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E79" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="F79" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>1.4</v>
+        <v>0.71</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="80">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="C80" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E80" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F80" t="n">
-        <v>1.4</v>
+        <v>0.45</v>
       </c>
       <c r="G80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I80" t="n">
         <v>1.8</v>
-      </c>
-      <c r="H80" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I80" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2919,28 +2919,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D81" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="E81" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F81" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="82">
@@ -2950,28 +2950,28 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.3</v>
+        <v>0.001</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D82" t="n">
-        <v>1.2</v>
+        <v>0.497</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F82" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="G82" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H82" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="83">
@@ -2981,28 +2981,28 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.95</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
@@ -3012,28 +3012,28 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="C84" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="D84" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E84" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="F84" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="85">
@@ -3043,28 +3043,28 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="D85" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="86">
@@ -3074,28 +3074,28 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="C86" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="D86" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F86" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G86" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="H86" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="87">
@@ -3105,28 +3105,28 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="D87" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="88">
@@ -3136,28 +3136,28 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D88" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3</v>
+        <v>0.95</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="89">
@@ -3167,28 +3167,28 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="D89" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="90">
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="C90" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F90" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H90" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3232,22 +3232,22 @@
         <v>0.8</v>
       </c>
       <c r="C91" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -3260,28 +3260,28 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C92" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="E92" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="F92" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="G92" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="H92" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="93">
@@ -3291,28 +3291,28 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E93" t="n">
-        <v>1.05</v>
+        <v>0.71</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.95</v>
+        <v>0.49</v>
       </c>
       <c r="H93" t="n">
-        <v>0.98</v>
+        <v>0.71</v>
       </c>
       <c r="I93" t="n">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="94">
@@ -3322,28 +3322,28 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="D94" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F94" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="95">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D95" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>1.2</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="H95" t="n">
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3384,28 +3384,28 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1.05</v>
+        <v>0.28</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D96" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="E96" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F96" t="n">
         <v>1.4</v>
       </c>
       <c r="G96" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H96" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="97">
@@ -3415,28 +3415,28 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="C97" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G97" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="98">
@@ -3446,25 +3446,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D98" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E98" t="n">
-        <v>1.3</v>
+        <v>0.97</v>
       </c>
       <c r="F98" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -3477,28 +3477,28 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="D99" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F99" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="100">
@@ -3511,25 +3511,25 @@
         <v>1.2</v>
       </c>
       <c r="C100" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D100" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G100" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="H100" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="101">
@@ -3539,28 +3539,28 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="C101" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F101" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="102">
@@ -3570,28 +3570,28 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="C102" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E102" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="F102" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G102" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H102" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -3601,28 +3601,28 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F103" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="G103" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="I103" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="104">
@@ -3632,28 +3632,28 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C104" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I104" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="105">
@@ -3666,25 +3666,25 @@
         <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="E105" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F105" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="106">
@@ -3694,28 +3694,28 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="C106" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D106" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E106" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="G106" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H106" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="107">
@@ -3725,28 +3725,28 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="D107" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="H107" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="108">
@@ -3756,28 +3756,28 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C108" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="D108" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="E108" t="n">
         <v>1.2</v>
       </c>
       <c r="F108" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G108" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="H108" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="109">
@@ -3787,28 +3787,28 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="D109" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>0.71</v>
       </c>
       <c r="F109" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G109" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H109" t="n">
-        <v>1.4</v>
+        <v>0.71</v>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="110">
@@ -3818,28 +3818,28 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="C110" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="D110" t="n">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="E110" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I110" t="n">
         <v>0.6</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3849,28 +3849,28 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="C111" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D111" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E111" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="112">
@@ -3880,28 +3880,28 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C112" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="113">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -3920,16 +3920,16 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F113" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H113" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="I113" t="n">
         <v>1.1</v>
@@ -3942,28 +3942,28 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C114" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="115">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -3982,19 +3982,19 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F115" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="116">
@@ -4004,28 +4004,28 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C116" t="n">
         <v>2.5</v>
       </c>
       <c r="D116" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F116" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H116" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="117">
@@ -4035,28 +4035,28 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C117" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E117" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="H117" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="118">
@@ -4066,28 +4066,28 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="C118" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D118" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H118" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="119">
@@ -4097,28 +4097,28 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
         <v>1.2</v>
       </c>
       <c r="E119" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H119" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="120">
@@ -4128,28 +4128,28 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="C120" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E120" t="n">
         <v>0.6</v>
       </c>
-      <c r="D120" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0.4</v>
-      </c>
       <c r="F120" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G120" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="H120" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="121">
@@ -4159,28 +4159,28 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="E121" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H121" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="122">
@@ -4190,28 +4190,28 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.1</v>
+        <v>0.25</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E122" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G122" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H122" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="123">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -4230,19 +4230,19 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>1.3</v>
+        <v>0.55</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="124">
@@ -4252,28 +4252,28 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="D124" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H124" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="125">
@@ -4289,22 +4289,22 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="126">
@@ -4314,28 +4314,28 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="C126" t="n">
         <v>0.7</v>
       </c>
       <c r="D126" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G126" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H126" t="n">
         <v>1.2</v>
       </c>
       <c r="I126" t="n">
-        <v>0.25</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="127">
@@ -4345,28 +4345,28 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="E127" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F127" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="128">
@@ -4376,28 +4376,28 @@
         </is>
       </c>
       <c r="B128" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C128" t="n">
         <v>0.9</v>
       </c>
-      <c r="C128" t="n">
-        <v>0.6</v>
-      </c>
       <c r="D128" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -4407,28 +4407,28 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C129" t="n">
         <v>1.4</v>
       </c>
       <c r="D129" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="F129" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I129" t="n">
         <v>0.65</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I129" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -4438,28 +4438,28 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="131">
@@ -4469,25 +4469,25 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C131" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E131" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F131" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H131" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I131" t="n">
         <v>0.8</v>
@@ -4500,28 +4500,28 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="C132" t="n">
         <v>0.95</v>
       </c>
       <c r="D132" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F132" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="G132" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H132" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="133">
@@ -4531,28 +4531,28 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="C133" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
@@ -4565,25 +4565,25 @@
         <v>1.2</v>
       </c>
       <c r="C134" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="D134" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="E134" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F134" t="n">
-        <v>2.2</v>
+        <v>0.36</v>
       </c>
       <c r="G134" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H134" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="135">
@@ -4593,28 +4593,28 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="C135" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="E135" t="n">
-        <v>1.05</v>
+        <v>0.25</v>
       </c>
       <c r="F135" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="136">
@@ -4624,28 +4624,28 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.05</v>
+        <v>0.1</v>
       </c>
       <c r="C136" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="D136" t="n">
-        <v>0.95</v>
+        <v>0.1</v>
       </c>
       <c r="E136" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="F136" t="n">
-        <v>1.1</v>
+        <v>0.65</v>
       </c>
       <c r="G136" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H136" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="137">
@@ -4655,28 +4655,28 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C137" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F137" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H137" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="138">
@@ -4686,19 +4686,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C138" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E138" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="F138" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="G138" t="n">
         <v>1.2</v>
@@ -4707,7 +4707,7 @@
         <v>0.7</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -4720,25 +4720,25 @@
         <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E139" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="F139" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
@@ -4748,28 +4748,28 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="C140" t="n">
         <v>0.4</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F140" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G140" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H140" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="141">
@@ -4779,28 +4779,28 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="C141" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D141" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="F141" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H141" t="n">
-        <v>0.95</v>
+        <v>0.27</v>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="142">
@@ -4810,25 +4810,25 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="C142" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="E142" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F142" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="G142" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H142" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="I142" t="n">
         <v>1.2</v>
@@ -4841,28 +4841,28 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.6</v>
+        <v>0.655</v>
       </c>
       <c r="C143" t="n">
         <v>1.4</v>
       </c>
       <c r="D143" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E143" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G143" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="H143" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="144">
@@ -4872,28 +4872,28 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F144" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="G144" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H144" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="145">
@@ -4903,28 +4903,28 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="C145" t="n">
-        <v>1.3</v>
+        <v>0.55</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E145" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G145" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="H145" t="n">
-        <v>1.3</v>
+        <v>0.28</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="146">
@@ -4934,16 +4934,16 @@
         </is>
       </c>
       <c r="B146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C146" t="n">
         <v>0.3</v>
       </c>
-      <c r="C146" t="n">
-        <v>0.35</v>
-      </c>
       <c r="D146" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="E146" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="F146" t="n">
         <v>0.3</v>
@@ -4952,10 +4952,10 @@
         <v>0.4</v>
       </c>
       <c r="H146" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="147">
@@ -4965,28 +4965,28 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.3</v>
+        <v>0.12</v>
       </c>
       <c r="C147" t="n">
-        <v>1.8</v>
+        <v>0.21</v>
       </c>
       <c r="D147" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F147" t="n">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="G147" t="n">
-        <v>1.2</v>
+        <v>0.18</v>
       </c>
       <c r="H147" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="148">
@@ -4996,28 +4996,28 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="C148" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="E148" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="F148" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H148" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="149">
@@ -5027,28 +5027,28 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="C149" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="D149" t="n">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="E149" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="F149" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G149" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="H149" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="150">
@@ -5058,28 +5058,28 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="C150" t="n">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="D150" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="E150" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="G150" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="151">
@@ -5089,28 +5089,28 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F151" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="152">
@@ -5120,28 +5120,28 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="C152" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F152" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="G152" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="H152" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>0.15</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="153">
@@ -5151,28 +5151,28 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="C153" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F153" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="G153" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H153" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="154">
@@ -5182,28 +5182,28 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="C154" t="n">
-        <v>1.2</v>
+        <v>0.571</v>
       </c>
       <c r="D154" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="H154" t="n">
         <v>0.7</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -5213,28 +5213,28 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="C155" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="156">
@@ -5244,28 +5244,28 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="C156" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E156" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H156" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="157">
@@ -5278,25 +5278,25 @@
         <v>1</v>
       </c>
       <c r="C157" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E157" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="158">
@@ -5306,28 +5306,28 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="C158" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="D158" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="G158" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H158" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="159">
@@ -5337,28 +5337,28 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C159" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="D159" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="E159" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="F159" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="G159" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="H159" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="160">
@@ -5368,28 +5368,28 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="C160" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E160" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H160" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="161">
@@ -5399,28 +5399,28 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="C161" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E161" t="n">
-        <v>3.2</v>
+        <v>0.36</v>
       </c>
       <c r="F161" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H161" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="162">
@@ -5430,28 +5430,28 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="C162" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D162" t="n">
         <v>0.6</v>
       </c>
-      <c r="D162" t="n">
-        <v>0.4</v>
-      </c>
       <c r="E162" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G162" t="n">
         <v>0.3</v>
       </c>
-      <c r="F162" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G162" t="n">
-        <v>1.3</v>
-      </c>
       <c r="H162" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="163">
@@ -5461,28 +5461,28 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.98</v>
+        <v>0.2</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="D163" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="E163" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="F163" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H163" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="164">
@@ -5492,28 +5492,28 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="C164" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D164" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="E164" t="n">
-        <v>1.1</v>
+        <v>0.35</v>
       </c>
       <c r="F164" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H164" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="165">
@@ -5523,25 +5523,25 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="C165" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E165" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="F165" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="I165" t="n">
         <v>1.2</v>
@@ -5554,28 +5554,28 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="C166" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="D166" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="E166" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F166" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H166" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
@@ -5585,28 +5585,28 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C167" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>1.2</v>
+        <v>0.35</v>
       </c>
       <c r="F167" t="n">
-        <v>0.97</v>
+        <v>3</v>
       </c>
       <c r="G167" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="H167" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I167" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="168">
@@ -5616,28 +5616,28 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C168" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="D168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F168" t="n">
         <v>2.5</v>
       </c>
-      <c r="E168" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F168" t="n">
-        <v>2</v>
-      </c>
       <c r="G168" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H168" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="169">
@@ -5647,28 +5647,28 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="C169" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E169" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="F169" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G169" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="170">
@@ -5678,28 +5678,28 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="E170" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="G170" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="H170" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="171">
@@ -5709,28 +5709,28 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="C171" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -5740,28 +5740,28 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.5</v>
+        <v>0.055</v>
       </c>
       <c r="C172" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="F172" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G172" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H172" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -5771,16 +5771,16 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="C173" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="I173" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -5802,28 +5802,28 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="C174" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D174" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E174" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F174" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="G174" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="H174" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="I174" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="175">
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C175" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="D175" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="E175" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="G175" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H175" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/archive/legacy_runs/lr_estimation_2025_07_21/est_lrs_by_category_plusminus_filled.xlsx
+++ b/archive/legacy_runs/lr_estimation_2025_07_21/est_lrs_by_category_plusminus_filled.xlsx
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="D2" t="n">
         <v>0.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="n">
         <v>0.4</v>
@@ -516,13 +516,13 @@
         <v>0.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.077</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="C4" t="n">
         <v>0.2</v>
@@ -541,19 +541,19 @@
         <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.25</v>
+        <v>0.052</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C6" t="n">
         <v>0.71</v>
@@ -603,16 +603,16 @@
         <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G6" t="n">
         <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
         <v>2.5</v>
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.35</v>
+        <v>1.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H8" t="n">
         <v>0.2</v>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="D9" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.75</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.057</v>
+        <v>0.2</v>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="C11" t="n">
-        <v>0.756</v>
+        <v>0.2</v>
       </c>
       <c r="D11" t="n">
         <v>0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.45</v>
+        <v>0.71</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.71</v>
+        <v>0.397</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C15" t="n">
         <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="E15" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0.4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0.599</v>
+        <v>0.65</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -975,16 +975,16 @@
         <v>0.71</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="I18" t="n">
         <v>1.4</v>
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C19" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
         <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="21">
@@ -1062,25 +1062,25 @@
         <v>0.3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.3</v>
       </c>
     </row>
     <row r="22">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -1121,25 +1121,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H23" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="I23" t="n">
         <v>0.3</v>
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H24" t="n">
         <v>2</v>
       </c>
-      <c r="C24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.4</v>
-      </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E25" t="n">
-        <v>0.71</v>
+        <v>0.24</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="C26" t="n">
         <v>0.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27">
@@ -1248,22 +1248,22 @@
         <v>0.5</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="E27" t="n">
         <v>0.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H27" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="I27" t="n">
         <v>0.4</v>
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="C28" t="n">
         <v>0.2</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.8</v>
+        <v>0.078</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="29">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.34</v>
+        <v>0.6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="F29" t="n">
         <v>0.4</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7</v>
+        <v>0.22</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I29" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="30">
@@ -1338,25 +1338,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="E30" t="n">
         <v>0.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G30" t="n">
-        <v>0.155</v>
+        <v>0.74</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I30" t="n">
         <v>1.4</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25</v>
+        <v>0.363</v>
       </c>
       <c r="C31" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32">
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F32" t="n">
         <v>0.4</v>
@@ -1418,7 +1418,7 @@
         <v>0.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="I32" t="n">
         <v>1.4</v>
@@ -1431,28 +1431,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E33" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D34" t="n">
         <v>0.8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F34" t="n">
         <v>1.4</v>
@@ -1480,7 +1480,7 @@
         <v>0.6</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>1.2</v>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.707</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1508,13 +1508,13 @@
         <v>0.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="36">
@@ -1524,13 +1524,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D36" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
         <v>0.5</v>
@@ -1539,10 +1539,10 @@
         <v>0.4</v>
       </c>
       <c r="G36" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I36" t="n">
         <v>1.2</v>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0.8</v>
@@ -1570,13 +1570,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="38">
@@ -1589,25 +1589,25 @@
         <v>1.2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="D38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.6</v>
       </c>
-      <c r="E38" t="n">
-        <v>0.2</v>
-      </c>
       <c r="F38" t="n">
         <v>0.4</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="39">
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -1648,28 +1648,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="E40" t="n">
         <v>0.71</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41">
@@ -1682,22 +1682,22 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F41" t="n">
-        <v>0.727</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I41" t="n">
         <v>0.8</v>
@@ -1710,28 +1710,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>2.5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="F42" t="n">
         <v>2.5</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H42" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1741,28 +1741,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -1772,28 +1772,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="C44" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E44" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0.8</v>
       </c>
       <c r="H44" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1812,19 +1812,19 @@
         <v>0.8</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G45" t="n">
         <v>0.8</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="46">
@@ -1834,28 +1834,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H46" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="47">
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C47" t="n">
-        <v>1.2</v>
+        <v>0.65</v>
       </c>
       <c r="D47" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F47" t="n">
         <v>0.4</v>
@@ -1883,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="48">
@@ -1896,28 +1896,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D48" t="n">
         <v>0.7</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H48" t="n">
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="49">
@@ -1939,16 +1939,16 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="50">
@@ -1961,16 +1961,16 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G50" t="n">
         <v>1.2</v>
@@ -1979,7 +1979,7 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="51">
@@ -1989,28 +1989,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C51" t="n">
         <v>0.7</v>
       </c>
       <c r="D51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I51" t="n">
         <v>0.65</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.75</v>
       </c>
     </row>
     <row r="52">
@@ -2020,22 +2020,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="D52" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G52" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H52" t="n">
         <v>0.8</v>
@@ -2051,28 +2051,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="54">
@@ -2085,25 +2085,25 @@
         <v>1.2</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>0.8</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G54" t="n">
         <v>1.5</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2113,28 +2113,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C55" t="n">
         <v>0.4</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H55" t="n">
-        <v>0.521</v>
+        <v>0.4</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="56">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="D56" t="n">
         <v>0.1</v>
@@ -2156,10 +2156,10 @@
         <v>0.2</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H56" t="n">
         <v>0.2</v>
@@ -2175,25 +2175,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C57" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E57" t="n">
         <v>0.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G57" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="H57" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="I57" t="n">
         <v>0.2</v>
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E58" t="n">
         <v>0.2</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G58" t="n">
         <v>0.2</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59">
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C59" t="n">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F59" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0.4</v>
@@ -2258,7 +2258,7 @@
         <v>0.4</v>
       </c>
       <c r="I59" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="C60" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E60" t="n">
         <v>1.2</v>
@@ -2283,13 +2283,13 @@
         <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H60" t="n">
         <v>1.2</v>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="61">
@@ -2302,25 +2302,25 @@
         <v>0.2</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.34</v>
+        <v>1.1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="G61" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H61" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="62">
@@ -2330,28 +2330,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="C62" t="n">
         <v>1.2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="G62" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="63">
@@ -2364,25 +2364,25 @@
         <v>0.2</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F63" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="64">
@@ -2392,28 +2392,28 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G64" t="n">
         <v>0.5</v>
       </c>
-      <c r="C64" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H64" t="n">
         <v>0.4</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="65">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C65" t="n">
         <v>1.2</v>
@@ -2432,19 +2432,19 @@
         <v>0.35</v>
       </c>
       <c r="E65" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F65" t="n">
         <v>0.3</v>
       </c>
-      <c r="F65" t="n">
-        <v>0.2</v>
-      </c>
       <c r="G65" t="n">
         <v>1.2</v>
       </c>
       <c r="H65" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="I65" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="66">
@@ -2454,28 +2454,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E66" t="n">
         <v>0.2</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H66" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="67">
@@ -2485,28 +2485,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C67" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E67" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F67" t="n">
         <v>1.2</v>
       </c>
       <c r="G67" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H67" t="n">
         <v>0.4</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="68">
@@ -2516,25 +2516,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I68" t="n">
         <v>1.2</v>
@@ -2553,22 +2553,22 @@
         <v>0.4</v>
       </c>
       <c r="D69" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H69" t="n">
-        <v>0.432</v>
+        <v>0.63</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="70">
@@ -2581,22 +2581,22 @@
         <v>1.2</v>
       </c>
       <c r="C70" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H70" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I70" t="n">
         <v>1.2</v>
@@ -2609,28 +2609,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="D71" t="n">
-        <v>0.75</v>
+        <v>0.377</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H71" t="n">
-        <v>1.2</v>
+        <v>0.22</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="72">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
@@ -2652,13 +2652,13 @@
         <v>0.8</v>
       </c>
       <c r="F72" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>1.4</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I72" t="n">
         <v>1.2</v>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C73" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
         <v>0.8</v>
       </c>
       <c r="E73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
         <v>0.71</v>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H73" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="74">
@@ -2702,28 +2702,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="D74" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F74" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H74" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2736,25 +2736,25 @@
         <v>0.75</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F75" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="76">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C76" t="n">
         <v>1.2</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G76" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H76" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>1.2</v>
@@ -2798,25 +2798,25 @@
         <v>0.8</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="E77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G77" t="n">
         <v>0.9</v>
       </c>
-      <c r="F77" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="78">
@@ -2829,7 +2829,7 @@
         <v>0.2</v>
       </c>
       <c r="C78" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D78" t="n">
         <v>0.4</v>
@@ -2838,16 +2838,16 @@
         <v>0.2</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H78" t="n">
         <v>0.2</v>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="79">
@@ -2857,28 +2857,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="D79" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="H79" t="n">
         <v>0.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="80">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8</v>
+        <v>0.781</v>
       </c>
       <c r="E80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F80" t="n">
         <v>0.6</v>
       </c>
-      <c r="F80" t="n">
-        <v>0.45</v>
-      </c>
       <c r="G80" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H80" t="n">
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="81">
@@ -2919,16 +2919,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="C81" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="D81" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="82">
@@ -2950,28 +2950,28 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.001</v>
+        <v>0.4</v>
       </c>
       <c r="C82" t="n">
-        <v>1.2</v>
+        <v>0.42</v>
       </c>
       <c r="D82" t="n">
-        <v>0.497</v>
+        <v>0.8</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H82" t="n">
-        <v>0.5</v>
+        <v>0.499</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="83">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -2990,19 +2990,19 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4</v>
+        <v>0.532</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="84">
@@ -3012,28 +3012,28 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F84" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H84" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="85">
@@ -3043,16 +3043,16 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="C85" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.537</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="86">
@@ -3074,25 +3074,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="C86" t="n">
         <v>2.5</v>
       </c>
       <c r="D86" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F86" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="G86" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I86" t="n">
         <v>1.4</v>
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C87" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -3123,10 +3123,10 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="88">
@@ -3136,28 +3136,28 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D88" t="n">
         <v>0.8</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F88" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="89">
@@ -3167,16 +3167,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C89" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -3185,10 +3185,10 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="90">
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
         <v>1.2</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
         <v>1.1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="92">
@@ -3260,13 +3260,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D92" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E92" t="n">
         <v>0.8</v>
@@ -3275,13 +3275,13 @@
         <v>0.7</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4</v>
+        <v>0.423</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6</v>
+        <v>0.471</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="93">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -3300,19 +3300,19 @@
         <v>0.8</v>
       </c>
       <c r="E93" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="H93" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -3322,28 +3322,28 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D94" t="n">
         <v>0.5</v>
       </c>
-      <c r="C94" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
       <c r="E94" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="F94" t="n">
         <v>1.4</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="95">
@@ -3353,25 +3353,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C95" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E95" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -3384,25 +3384,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="C96" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D96" t="n">
         <v>0.8</v>
       </c>
       <c r="E96" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G96" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H96" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="I96" t="n">
         <v>1.2</v>
@@ -3415,28 +3415,28 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C97" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D97" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F97" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="G97" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="H97" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="98">
@@ -3446,28 +3446,28 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="C98" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>0.7</v>
       </c>
       <c r="E98" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="99">
@@ -3477,28 +3477,28 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="C99" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F99" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="100">
@@ -3508,25 +3508,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F100" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
         <v>3.2</v>
       </c>
       <c r="H100" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I100" t="n">
         <v>1.2</v>
@@ -3539,28 +3539,28 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E101" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="102">
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D102" t="n">
         <v>0.8</v>
@@ -3582,16 +3582,16 @@
         <v>0.8</v>
       </c>
       <c r="F102" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H102" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="103">
@@ -3601,25 +3601,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C103" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="D103" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F103" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H103" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
         <v>0.8</v>
@@ -3632,28 +3632,28 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="C104" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D104" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E104" t="n">
         <v>0.71</v>
       </c>
-      <c r="E104" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0.743</v>
       </c>
       <c r="G104" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H104" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="105">
@@ -3669,22 +3669,22 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="E105" t="n">
         <v>0.8</v>
       </c>
       <c r="F105" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="G105" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="H105" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="I105" t="n">
-        <v>0.84</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="106">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D106" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F106" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="G106" t="n">
         <v>1.4</v>
@@ -3725,28 +3725,28 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="C107" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="D107" t="n">
         <v>0.8</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G107" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="H107" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="108">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C108" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D108" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E108" t="n">
         <v>1.2</v>
@@ -3774,7 +3774,7 @@
         <v>1.2</v>
       </c>
       <c r="H108" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="I108" t="n">
         <v>1.2</v>
@@ -3787,28 +3787,28 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C109" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E109" t="n">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G109" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H109" t="n">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="110">
@@ -3818,28 +3818,28 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C110" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="D110" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="G110" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H110" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="111">
@@ -3849,22 +3849,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="C111" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
@@ -3880,28 +3880,28 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
         <v>0.8</v>
       </c>
       <c r="E112" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="F112" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G112" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="113">
@@ -3911,28 +3911,28 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E113" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="F113" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="G113" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H113" t="n">
         <v>0.4</v>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3942,28 +3942,28 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E114" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F114" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H114" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="115">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -3982,19 +3982,19 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="116">
@@ -4010,19 +4010,19 @@
         <v>2.5</v>
       </c>
       <c r="D116" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="E116" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F116" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G116" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H116" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="I116" t="n">
         <v>1.2</v>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C117" t="n">
         <v>0.4</v>
       </c>
       <c r="D117" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -4050,13 +4050,13 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n">
         <v>0.71</v>
-      </c>
-      <c r="H117" t="n">
-        <v>1</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="118">
@@ -4066,25 +4066,25 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="C118" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E118" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G118" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I118" t="n">
         <v>1.2</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -4106,19 +4106,19 @@
         <v>1.2</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="120">
@@ -4128,28 +4128,28 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C120" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D120" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E120" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F120" t="n">
         <v>0.4</v>
       </c>
       <c r="G120" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H120" t="n">
         <v>0.4</v>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="121">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -4168,19 +4168,19 @@
         <v>0.8</v>
       </c>
       <c r="E121" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H121" t="n">
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="122">
@@ -4190,22 +4190,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="C122" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="D122" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E122" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="F122" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G122" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H122" t="n">
         <v>1.4</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -4239,10 +4239,10 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="I123" t="n">
-        <v>0.75</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="124">
@@ -4252,28 +4252,28 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C124" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D124" t="n">
         <v>0.5</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G124" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="H124" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="125">
@@ -4283,28 +4283,28 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0.708</v>
       </c>
       <c r="E125" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H125" t="n">
         <v>0.4</v>
       </c>
       <c r="I125" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="126">
@@ -4314,22 +4314,22 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C126" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D126" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E126" t="n">
         <v>0.3</v>
       </c>
-      <c r="E126" t="n">
-        <v>0.2</v>
-      </c>
       <c r="F126" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H126" t="n">
         <v>1.2</v>
@@ -4345,25 +4345,25 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E127" t="n">
         <v>0.3</v>
       </c>
       <c r="F127" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H127" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="I127" t="n">
         <v>0.4</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="n">
         <v>0.9</v>
       </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1</v>
-      </c>
       <c r="H128" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -4407,28 +4407,28 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="C129" t="n">
-        <v>1.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E129" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H129" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I129" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="130">
@@ -4447,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -4456,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I130" t="n">
         <v>1.2</v>
@@ -4469,22 +4469,22 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E131" t="n">
         <v>0.75</v>
       </c>
-      <c r="C131" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E131" t="n">
-        <v>1.2</v>
-      </c>
       <c r="F131" t="n">
-        <v>0.4</v>
+        <v>0.737</v>
       </c>
       <c r="G131" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H131" t="n">
         <v>0.8</v>
@@ -4500,22 +4500,22 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C132" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F132" t="n">
         <v>0.5</v>
       </c>
       <c r="G132" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H132" t="n">
         <v>0.2</v>
@@ -4531,19 +4531,19 @@
         </is>
       </c>
       <c r="B133" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
         <v>0.75</v>
       </c>
-      <c r="C133" t="n">
-        <v>1</v>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
       <c r="E133" t="n">
         <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -4552,7 +4552,7 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="134">
@@ -4562,25 +4562,25 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E134" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="G134" t="n">
         <v>0.8</v>
       </c>
       <c r="H134" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I134" t="n">
         <v>1.4</v>
@@ -4593,28 +4593,28 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="E135" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D136" t="n">
         <v>0.1</v>
@@ -4636,16 +4636,16 @@
         <v>0.4</v>
       </c>
       <c r="F136" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G136" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H136" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="137">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -4664,13 +4664,13 @@
         <v>0.8</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H137" t="n">
         <v>0.4</v>
@@ -4686,28 +4686,28 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C138" t="n">
         <v>0.7</v>
       </c>
       <c r="D138" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F138" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G138" t="n">
         <v>1.2</v>
       </c>
       <c r="H138" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="139">
@@ -4717,28 +4717,28 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="E139" t="n">
         <v>0.4</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="140">
@@ -4748,28 +4748,28 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D140" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F140" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H140" t="n">
-        <v>2</v>
+        <v>0.707</v>
       </c>
       <c r="I140" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="141">
@@ -4779,25 +4779,25 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="G141" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H141" t="n">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="I141" t="n">
         <v>0.4</v>
@@ -4813,7 +4813,7 @@
         <v>1.2</v>
       </c>
       <c r="C142" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="D142" t="n">
         <v>1.4</v>
@@ -4825,10 +4825,10 @@
         <v>1.4</v>
       </c>
       <c r="G142" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H142" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
         <v>1.2</v>
@@ -4841,28 +4841,28 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.655</v>
+        <v>0.3</v>
       </c>
       <c r="C143" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D143" t="n">
         <v>0.4</v>
       </c>
       <c r="E143" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="F143" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G143" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="144">
@@ -4872,28 +4872,28 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E144" t="n">
         <v>1.2</v>
       </c>
       <c r="F144" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="G144" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H144" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="145">
@@ -4903,25 +4903,25 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C145" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G145" t="n">
         <v>0.55</v>
       </c>
-      <c r="D145" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H145" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="I145" t="n">
         <v>0.4</v>
@@ -4934,16 +4934,16 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E146" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
         <v>0.3</v>
@@ -4952,10 +4952,10 @@
         <v>0.4</v>
       </c>
       <c r="H146" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="147">
@@ -4965,19 +4965,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="C147" t="n">
-        <v>0.21</v>
+        <v>1.2</v>
       </c>
       <c r="D147" t="n">
         <v>0.3</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F147" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G147" t="n">
         <v>0.18</v>
@@ -4996,25 +4996,25 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D148" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F148" t="n">
         <v>0.6</v>
       </c>
-      <c r="E148" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0.8</v>
-      </c>
       <c r="G148" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H148" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="I148" t="n">
         <v>1.2</v>
@@ -5030,25 +5030,25 @@
         <v>0.4</v>
       </c>
       <c r="C149" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="D149" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="n">
         <v>0.5</v>
       </c>
-      <c r="E149" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H149" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="150">
@@ -5061,25 +5061,25 @@
         <v>0.8</v>
       </c>
       <c r="C150" t="n">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="D150" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E150" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G150" t="n">
         <v>0.9</v>
       </c>
-      <c r="F150" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
       <c r="H150" t="n">
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="151">
@@ -5089,16 +5089,16 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
@@ -5107,10 +5107,10 @@
         <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="152">
@@ -5120,28 +5120,28 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D152" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E152" t="n">
         <v>0.8</v>
       </c>
       <c r="F152" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="153">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -5160,16 +5160,16 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F153" t="n">
         <v>0.4</v>
       </c>
       <c r="G153" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="I153" t="n">
         <v>0.4</v>
@@ -5182,28 +5182,28 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C154" t="n">
-        <v>0.571</v>
+        <v>0.68</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E154" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="F154" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H154" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="155">
@@ -5213,16 +5213,16 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E155" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
@@ -5231,10 +5231,10 @@
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -5247,22 +5247,22 @@
         <v>0.1</v>
       </c>
       <c r="C156" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H156" t="n">
         <v>0.3</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0.2</v>
       </c>
       <c r="I156" t="n">
         <v>1.2</v>
@@ -5275,16 +5275,16 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E157" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
@@ -5296,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="158">
@@ -5309,25 +5309,25 @@
         <v>0.1</v>
       </c>
       <c r="C158" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="D158" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E158" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F158" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="G158" t="n">
         <v>0.4</v>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="159">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C159" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D159" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E159" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H159" t="n">
         <v>0.2</v>
@@ -5368,28 +5368,28 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="C160" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="D160" t="n">
         <v>0.8</v>
       </c>
       <c r="E160" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F160" t="n">
         <v>0.2</v>
       </c>
       <c r="G160" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H160" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="161">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -5408,19 +5408,19 @@
         <v>0.8</v>
       </c>
       <c r="E161" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="F161" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="G161" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I161" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="162">
@@ -5430,28 +5430,28 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="C162" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="D162" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E162" t="n">
         <v>0.2</v>
       </c>
       <c r="F162" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="G162" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H162" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="163">
@@ -5467,22 +5467,22 @@
         <v>0.71</v>
       </c>
       <c r="D163" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E163" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="164">
@@ -5495,25 +5495,25 @@
         <v>0.2</v>
       </c>
       <c r="C164" t="n">
-        <v>0.5</v>
+        <v>0.426</v>
       </c>
       <c r="D164" t="n">
         <v>0.2</v>
       </c>
       <c r="E164" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F164" t="n">
         <v>0.4</v>
       </c>
       <c r="G164" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H164" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="165">
@@ -5523,25 +5523,25 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
         <v>1.2</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7</v>
+        <v>0.721</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="I165" t="n">
         <v>1.2</v>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C166" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E166" t="n">
         <v>0.2</v>
@@ -5572,10 +5572,10 @@
         <v>0.2</v>
       </c>
       <c r="H166" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="I166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -5585,28 +5585,28 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C167" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -5619,13 +5619,13 @@
         <v>0.1</v>
       </c>
       <c r="C168" t="n">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="D168" t="n">
         <v>1.4</v>
       </c>
       <c r="E168" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F168" t="n">
         <v>2.5</v>
@@ -5637,7 +5637,7 @@
         <v>3.2</v>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -5647,28 +5647,28 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D169" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I169" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="170">
@@ -5678,28 +5678,28 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.54</v>
+        <v>0.05</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D170" t="n">
         <v>0.25</v>
       </c>
       <c r="E170" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F170" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="G170" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="H170" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="171">
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -5721,16 +5721,16 @@
         <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="172">
@@ -5743,25 +5743,25 @@
         <v>0.055</v>
       </c>
       <c r="C172" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="D172" t="n">
         <v>0.1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G172" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="H172" t="n">
         <v>0.2</v>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="173">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.2</v>
+        <v>0.74</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -5789,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I173" t="n">
         <v>1</v>
@@ -5802,25 +5802,25 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="C174" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D174" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F174" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="G174" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H174" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I174" t="n">
         <v>1.4</v>
@@ -5833,28 +5833,28 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="C175" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="D175" t="n">
         <v>0.8</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F175" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G175" t="n">
         <v>0.4</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
